--- a/europe/_gas/Gas_Sectors_Dataset.xlsx
+++ b/europe/_gas/Gas_Sectors_Dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papo002\Desktop\Work\1_MOPO\WP2\Gas_Sector\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7097A0CD-CC54-4C9D-A552-551A01BE8D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2C4410-72A6-49BF-9D25-CA2CA0A39D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="894" activeTab="6" xr2:uid="{8EFE3EAE-CE21-4F90-AC97-5C3E007313D2}"/>
+    <workbookView xWindow="384" yWindow="1104" windowWidth="23040" windowHeight="12120" tabRatio="894" xr2:uid="{8EFE3EAE-CE21-4F90-AC97-5C3E007313D2}"/>
   </bookViews>
   <sheets>
     <sheet name="CH4_Production" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="146">
   <si>
     <t>Year</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t xml:space="preserve">Capacity 2030 (GWh/d) </t>
+  </si>
+  <si>
+    <t>https://ens.dk/en/analyses-and-statistics/technology-data-carbon-capture-transport-and-storage</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1537,7 @@
         <v>669</v>
       </c>
       <c r="E2" s="69">
-        <v>1.1100000000000001</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1551,7 +1554,7 @@
         <v>85.5</v>
       </c>
       <c r="E3" s="69">
-        <v>1.93</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1568,7 +1571,7 @@
         <v>40</v>
       </c>
       <c r="E4" s="69">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1585,7 +1588,7 @@
         <v>144.80000000000001</v>
       </c>
       <c r="E5" s="69">
-        <v>1.3900000000000001</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1602,7 +1605,7 @@
         <v>1481</v>
       </c>
       <c r="E6" s="69">
-        <v>1.61</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1619,7 +1622,7 @@
         <v>500.4</v>
       </c>
       <c r="E7" s="69">
-        <v>2.91</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1636,7 +1639,7 @@
         <v>224.6</v>
       </c>
       <c r="E8" s="69">
-        <v>1.69</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1653,7 +1656,7 @@
         <v>723.1</v>
       </c>
       <c r="E9" s="69">
-        <v>3.27</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1670,7 +1673,7 @@
         <v>122</v>
       </c>
       <c r="E10" s="69">
-        <v>1.7999999999999998</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1687,7 +1690,7 @@
         <v>22.437999999999999</v>
       </c>
       <c r="E11" s="69">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1704,7 +1707,7 @@
         <v>860.3</v>
       </c>
       <c r="E12" s="69">
-        <v>2.21</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1721,7 +1724,7 @@
         <v>227.304</v>
       </c>
       <c r="E13" s="69">
-        <v>2.63</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1738,7 +1741,7 @@
         <v>200</v>
       </c>
       <c r="E14" s="69">
-        <v>1.1800000000000002</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1755,7 +1758,7 @@
         <v>1910.4281840000001</v>
       </c>
       <c r="E15" s="69">
-        <v>1.4700000000000002</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1772,7 +1775,7 @@
         <v>1616.4469999999999</v>
       </c>
       <c r="E16" s="69">
-        <v>2.5700000000000003</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -8853,7 +8856,7 @@
     <col min="1" max="1" width="22.21875" customWidth="1"/>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
     <col min="3" max="3" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="51.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="85.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -9304,7 +9307,7 @@
         <v>0.91</v>
       </c>
       <c r="G21" s="59" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -9349,7 +9352,7 @@
     <hyperlink ref="G16" r:id="rId13" display="https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels" xr:uid="{104FE274-B953-4764-870A-9D095150285F}"/>
     <hyperlink ref="G17" r:id="rId14" display="https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels" xr:uid="{620B23C9-B43D-4F2F-BAC1-C2A66989B97A}"/>
     <hyperlink ref="G20" r:id="rId15" display="https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels" xr:uid="{1C9BEA98-2367-4C62-8FE8-56967553ED7C}"/>
-    <hyperlink ref="G21" r:id="rId16" display="https://ens.dk/en/analyses-and-statistics/technology-data-renewable-fuels" xr:uid="{0CD7082E-A035-4922-A9CD-B4BAE88EDB03}"/>
+    <hyperlink ref="G21" r:id="rId16" xr:uid="{0CD7082E-A035-4922-A9CD-B4BAE88EDB03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId17"/>
